--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554809259</v>
+        <v>46157.93111037948</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111037948</v>
+        <v>46157.93135088119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93135088119</v>
+        <v>46157.93382576034</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93382576034</v>
+        <v>46157.93694564722</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93694564722</v>
+        <v>46158.28204427267</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204427267</v>
+        <v>46158.2965146162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2965146162</v>
+        <v>46158.2980633717</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980633717</v>
+        <v>46158.33369461553</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369461553</v>
+        <v>46158.37221055834</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221055834</v>
+        <v>46158.37274996965</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
